--- a/tests/fixtures/agc-room-inventory-integration.xlsx
+++ b/tests/fixtures/agc-room-inventory-integration.xlsx
@@ -4,67 +4,74 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Room inventory" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Hostels without heater" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="WASL" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="GGL" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="EBPV" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Instructions" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
-  <si>
-    <t>Accommodation location</t>
-  </si>
-  <si>
-    <t>Building / block</t>
-  </si>
-  <si>
-    <t>Room number or apartment name</t>
-  </si>
-  <si>
-    <t>Room capacity (beds/delegates)</t>
-  </si>
-  <si>
-    <t>Gender designation (blank = any)</t>
-  </si>
-  <si>
-    <t>Mighty Fortress Dormitories</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
+  <si>
+    <t>HOSTEL WITHOUT HEATER</t>
+  </si>
+  <si>
+    <t>NO. OF ROOMS</t>
+  </si>
+  <si>
+    <t>ROOM NUMBER</t>
+  </si>
+  <si>
+    <t>CAPACITY</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Dorm Hall 1</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Hostels Blocks 1–4</t>
-  </si>
-  <si>
-    <t>Block 1</t>
+    <t>WISE AS SERPENTS</t>
+  </si>
+  <si>
+    <t>ADDITONAL INFORMATION</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>HAS FRIDGE</t>
+  </si>
+  <si>
+    <t>GOOD GENERAL</t>
+  </si>
+  <si>
+    <t>Capacity</t>
   </si>
   <si>
     <t>Room 101</t>
   </si>
   <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Wise as Serpents Lodge</t>
-  </si>
-  <si>
-    <t>WSL Room 1</t>
-  </si>
-  <si>
-    <t>Good General Lodge</t>
-  </si>
-  <si>
-    <t>GGL Room 1</t>
-  </si>
-  <si>
-    <t>Everything by Prayer Village</t>
+    <t>EVERYTHING BY PRAYER VILLAGE</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Apartment name</t>
   </si>
   <si>
     <t>Apartment 1</t>
@@ -73,26 +80,20 @@
     <t>Apartment 2</t>
   </si>
   <si>
-    <t>Not A Real Location</t>
-  </si>
-  <si>
-    <t>Room X</t>
+    <t>One sheet per accommodation type. Keep the title and header rows, then add one room per row. NO. OF ROOMS is only a count and is ignored.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -115,9 +116,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,150 +457,294 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>16</v>
       </c>
-      <c r="D5">
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
         <v>5</v>
       </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>21</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
